--- a/artfynd/A 62145-2025 artfynd.xlsx
+++ b/artfynd/A 62145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130292233</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130292188</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62145-2025 artfynd.xlsx
+++ b/artfynd/A 62145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130292233</v>
       </c>
       <c r="B2" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130292188</v>
       </c>
       <c r="B3" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62145-2025 artfynd.xlsx
+++ b/artfynd/A 62145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130292233</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130292188</v>
       </c>
       <c r="B3" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62145-2025 artfynd.xlsx
+++ b/artfynd/A 62145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130292233</v>
       </c>
       <c r="B2" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130292188</v>
       </c>
       <c r="B3" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62145-2025 artfynd.xlsx
+++ b/artfynd/A 62145-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130292233</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130292188</v>
       </c>
       <c r="B3" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62145-2025 artfynd.xlsx
+++ b/artfynd/A 62145-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130292233</v>
+        <v>130292188</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>767709</v>
+        <v>767702</v>
       </c>
       <c r="R2" t="n">
-        <v>7085139</v>
+        <v>7085134</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -771,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130292188</v>
+        <v>130292233</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767702</v>
+        <v>767709</v>
       </c>
       <c r="R3" t="n">
-        <v>7085134</v>
+        <v>7085139</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -883,21 +898,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 62145-2025 artfynd.xlsx
+++ b/artfynd/A 62145-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130292188</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,8 +921,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130292233</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>